--- a/output/yearly_surface_area_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_44_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497638673182</v>
+        <v>10.84497624940887</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907213187189</v>
+        <v>37.78907165337321</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.497787143782138</v>
+        <v>6.994952392758523</v>
       </c>
       <c r="C2" t="n">
-        <v>7.28554971321558</v>
+        <v>6.929175296573987</v>
       </c>
       <c r="D2" t="n">
-        <v>22.60081389946582</v>
+        <v>19.27661617288612</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.30406405087603</v>
+        <v>20.41053477129119</v>
       </c>
       <c r="C3" t="n">
-        <v>29.94330497952772</v>
+        <v>31.17048960983623</v>
       </c>
       <c r="D3" t="n">
-        <v>67.54424205218055</v>
+        <v>75.99708978574559</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.81822211046087</v>
+        <v>39.79416144394021</v>
       </c>
       <c r="C4" t="n">
-        <v>64.27305870163018</v>
+        <v>71.63714823118551</v>
       </c>
       <c r="D4" t="n">
-        <v>94.91634979428588</v>
+        <v>110.2699021410017</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.01188845010476</v>
+        <v>51.5908418581699</v>
       </c>
       <c r="C5" t="n">
-        <v>113.9563647704485</v>
+        <v>114.1527143112979</v>
       </c>
       <c r="D5" t="n">
-        <v>72.5511553438393</v>
+        <v>82.46680715673209</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>47.37619896383834</v>
       </c>
       <c r="C6" t="n">
-        <v>137.2581465307466</v>
+        <v>115.7637622939669</v>
       </c>
       <c r="D6" t="n">
-        <v>48.26173539306896</v>
+        <v>54.017722183068</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>32.87774886752143</v>
       </c>
       <c r="C7" t="n">
-        <v>128.2172319223377</v>
+        <v>104.2625879387155</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="C8" t="n">
-        <v>84.86718029361552</v>
+        <v>74.01886816168827</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>46.03905859065416</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
         <v>33.9468721174462</v>
@@ -895,7 +895,7 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.67176977909633</v>
+        <v>7.659494467383225</v>
       </c>
       <c r="C21" t="n">
-        <v>94.93815101631709</v>
+        <v>92.87137041702161</v>
       </c>
       <c r="D21" t="n">
-        <v>7.67176977909633</v>
+        <v>7.659494467383225</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.32794479094744</v>
+        <v>7.339545836949155</v>
       </c>
       <c r="C2" t="n">
-        <v>10.13556329864407</v>
+        <v>5.354451978962104</v>
       </c>
       <c r="D2" t="n">
-        <v>32.22685013960579</v>
+        <v>16.12422429454961</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.2037458585936</v>
+        <v>21.90279128174634</v>
       </c>
       <c r="C3" t="n">
-        <v>28.93701358267474</v>
+        <v>28.83883881225006</v>
       </c>
       <c r="D3" t="n">
-        <v>69.18376071827272</v>
+        <v>73.66053024963819</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.72062817711294</v>
+        <v>38.76038111136832</v>
       </c>
       <c r="C4" t="n">
-        <v>68.70172259548755</v>
+        <v>74.55981114672825</v>
       </c>
       <c r="D4" t="n">
-        <v>105.1903395192287</v>
+        <v>121.1565024333946</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>54.97787143782139</v>
       </c>
       <c r="C5" t="n">
-        <v>116.0180349493668</v>
+        <v>121.3194725522996</v>
       </c>
       <c r="D5" t="n">
-        <v>86.54106012935635</v>
+        <v>99.05834335850319</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.38499363544755</v>
+        <v>57.27810630887167</v>
       </c>
       <c r="C6" t="n">
-        <v>156.4984380385756</v>
+        <v>146.1940141348011</v>
       </c>
       <c r="D6" t="n">
-        <v>58.44540432922113</v>
+        <v>65.73095404243671</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.95570784678443</v>
+        <v>43.83699849002857</v>
       </c>
       <c r="C7" t="n">
-        <v>161.6339602794906</v>
+        <v>132.4691812294306</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>45.75337000871835</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.44489594093983</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="C8" t="n">
-        <v>123.5038611942487</v>
+        <v>103.9768993567797</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>11.87031149204818</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>64.23280704575605</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.849329104748648</v>
+        <v>7.834132639644568</v>
       </c>
       <c r="C21" t="n">
-        <v>103.022444499826</v>
+        <v>100.8644577354238</v>
       </c>
       <c r="D21" t="n">
-        <v>8.830495242842229</v>
+        <v>8.813399219600139</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.391578465274236</v>
+        <v>8.49506288484765</v>
       </c>
       <c r="C2" t="n">
-        <v>7.866744354129692</v>
+        <v>5.238605749860979</v>
       </c>
       <c r="D2" t="n">
-        <v>29.95901294279567</v>
+        <v>20.78752588972196</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.58171872472863</v>
+        <v>22.61455836732528</v>
       </c>
       <c r="C3" t="n">
-        <v>33.52177536150734</v>
+        <v>25.13764996723958</v>
       </c>
       <c r="D3" t="n">
-        <v>75.78601402933252</v>
+        <v>69.77771807934205</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>39.07944911524854</v>
       </c>
       <c r="C4" t="n">
-        <v>69.42919764433444</v>
+        <v>72.46672504127406</v>
       </c>
       <c r="D4" t="n">
-        <v>111.7376149588507</v>
+        <v>126.440268577651</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.39891802975625</v>
+        <v>55.86144437164352</v>
       </c>
       <c r="C5" t="n">
-        <v>120.3868122332651</v>
+        <v>126.7190849256571</v>
       </c>
       <c r="D5" t="n">
-        <v>100.5555086074796</v>
+        <v>115.3308115563941</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.0944373727195</v>
+        <v>64.08063615159783</v>
       </c>
       <c r="C6" t="n">
-        <v>167.1651268452172</v>
+        <v>166.1588354483642</v>
       </c>
       <c r="D6" t="n">
-        <v>68.30706001838034</v>
+        <v>77.20267596656069</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.78278138211675</v>
+        <v>54.25726862290422</v>
       </c>
       <c r="C7" t="n">
-        <v>190.139986620001</v>
+        <v>164.4486309475662</v>
       </c>
       <c r="D7" t="n">
-        <v>48.98724694650735</v>
+        <v>52.4007837141735</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.45457454926205</v>
+        <v>34.04701038327938</v>
       </c>
       <c r="C8" t="n">
-        <v>161.0557108816892</v>
+        <v>133.6845848872882</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C9" t="n">
-        <v>106.3890534661141</v>
+        <v>91.74530470956864</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>60.78490910844128</v>
+        <v>54.23665192111504</v>
       </c>
       <c r="D10" t="n">
         <v>35.87306111317846</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>37.6716229073586</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.010818687994295</v>
+        <v>7.993800603895563</v>
       </c>
       <c r="C21" t="n">
-        <v>111.1501092959209</v>
+        <v>108.915533228077</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01352335999287</v>
+        <v>9.992250754869454</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.65428593938488</v>
+        <v>7.806857744170636</v>
       </c>
       <c r="C2" t="n">
-        <v>5.411393345808419</v>
+        <v>3.603995822290041</v>
       </c>
       <c r="D2" t="n">
-        <v>24.69390000492002</v>
+        <v>17.29937629653305</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.75276380944582</v>
+        <v>27.06187546756333</v>
       </c>
       <c r="C3" t="n">
-        <v>47.60494617892783</v>
+        <v>38.56795856133595</v>
       </c>
       <c r="D3" t="n">
-        <v>82.31463626257381</v>
+        <v>78.57417750939346</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.39933463591698</v>
+        <v>26.84000048640355</v>
       </c>
       <c r="C4" t="n">
-        <v>98.0815043927776</v>
+        <v>102.9058126114464</v>
       </c>
       <c r="D4" t="n">
-        <v>109.0829691665673</v>
+        <v>123.9898263078509</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.53173170727006</v>
+        <v>36.10377182367646</v>
       </c>
       <c r="C5" t="n">
-        <v>99.86828521450681</v>
+        <v>99.27923659195872</v>
       </c>
       <c r="D5" t="n">
-        <v>67.83876636345461</v>
+        <v>77.11628216858696</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.318291544821</v>
+        <v>33.6906359666378</v>
       </c>
       <c r="C6" t="n">
-        <v>125.2229014243849</v>
+        <v>108.3172059572549</v>
       </c>
       <c r="D6" t="n">
-        <v>32.24157635516951</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>22.51736534460484</v>
       </c>
       <c r="C7" t="n">
-        <v>113.2455794325738</v>
+        <v>93.96209102575797</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>78.35819301445918</v>
+        <v>67.59332943739288</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>46.37187106239383</v>
+        <v>41.3796839862988</v>
       </c>
       <c r="D9" t="n">
         <v>27.29062268265283</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.944662275663684</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C2" t="n">
-        <v>3.507784547273853</v>
+        <v>1.867284133477433</v>
       </c>
       <c r="D2" t="n">
-        <v>18.39697022988098</v>
+        <v>11.93314334511998</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.75062038758809</v>
+        <v>27.70492021384499</v>
       </c>
       <c r="C3" t="n">
-        <v>34.80295611554943</v>
+        <v>26.60045404656733</v>
       </c>
       <c r="D3" t="n">
-        <v>83.95906366718722</v>
+        <v>75.87928006123597</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.26117025152543</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="C4" t="n">
-        <v>111.6355131976091</v>
+        <v>102.510168286635</v>
       </c>
       <c r="D4" t="n">
-        <v>121.9222656427071</v>
+        <v>132.9620185769625</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.25608158655496</v>
+        <v>40.00621894805753</v>
       </c>
       <c r="C5" t="n">
-        <v>137.3955912093411</v>
+        <v>142.6724851196678</v>
       </c>
       <c r="D5" t="n">
-        <v>84.77391426171209</v>
+        <v>96.38308086443064</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="C6" t="n">
-        <v>146.1537624789269</v>
+        <v>133.7562524696982</v>
       </c>
       <c r="D6" t="n">
-        <v>40.37241084174159</v>
+        <v>43.91455655866408</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="C7" t="n">
-        <v>141.3922861133299</v>
+        <v>119.0545805986022</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>103.4762080276138</v>
+        <v>88.45546815263761</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>51.36405813848885</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
         <v>28.28906009787183</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.492076584005904</v>
+        <v>5.78347572571796</v>
       </c>
       <c r="C2" t="n">
-        <v>9.439504176333081</v>
+        <v>2.819579406596839</v>
       </c>
       <c r="D2" t="n">
-        <v>16.312719853765</v>
+        <v>11.06626012227005</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>22.25131171675396</v>
       </c>
       <c r="C3" t="n">
-        <v>23.52267499375358</v>
+        <v>16.39518666092173</v>
       </c>
       <c r="D3" t="n">
-        <v>79.40375431948202</v>
+        <v>68.57507714163971</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>44.65675782307466</v>
       </c>
       <c r="C4" t="n">
-        <v>98.94936936333177</v>
+        <v>84.0425122220482</v>
       </c>
       <c r="D4" t="n">
-        <v>133.9319853087584</v>
+        <v>139.4071922553428</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.26299487821369</v>
+        <v>47.61476365597031</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1985473248906</v>
+        <v>165.3017697025567</v>
       </c>
       <c r="D5" t="n">
-        <v>105.1697228174396</v>
+        <v>117.9078992800419</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.73717901936489</v>
+        <v>46.77242412572655</v>
       </c>
       <c r="C6" t="n">
-        <v>179.6833918220682</v>
+        <v>178.9588620163341</v>
       </c>
       <c r="D6" t="n">
-        <v>54.017722183068</v>
+        <v>59.73345731719294</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>31.38058361854505</v>
       </c>
       <c r="C7" t="n">
-        <v>175.4677671800324</v>
+        <v>154.6272269142811</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C8" t="n">
-        <v>142.0294403733861</v>
+        <v>120.3328161095315</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>83.86874287839649</v>
+        <v>73.1078062921472</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.062651926622549</v>
+        <v>3.435135217159589</v>
       </c>
       <c r="C2" t="n">
-        <v>4.411974182885166</v>
+        <v>1.334195130071415</v>
       </c>
       <c r="D2" t="n">
-        <v>11.38140113533327</v>
+        <v>7.7410806479861</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.06277509980957</v>
+        <v>23.01216618754523</v>
       </c>
       <c r="C3" t="n">
-        <v>30.75815557405257</v>
+        <v>15.12382338392211</v>
       </c>
       <c r="D3" t="n">
-        <v>77.84768420825083</v>
+        <v>65.65928646002668</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.44582093538184</v>
+        <v>49.51935420220912</v>
       </c>
       <c r="C4" t="n">
-        <v>94.04848482373168</v>
+        <v>76.8443380545106</v>
       </c>
       <c r="D4" t="n">
-        <v>143.0700929398877</v>
+        <v>145.8013150531023</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.27557767191965</v>
+        <v>49.94641445355649</v>
       </c>
       <c r="C5" t="n">
-        <v>203.6635612460009</v>
+        <v>188.6428213710246</v>
       </c>
       <c r="D5" t="n">
-        <v>110.9129468872834</v>
+        <v>123.7002107350981</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>38.48058301565798</v>
       </c>
       <c r="C6" t="n">
-        <v>217.1979350967474</v>
+        <v>214.7828357443002</v>
       </c>
       <c r="D6" t="n">
-        <v>52.85042416271855</v>
+        <v>58.00263611460582</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>184.0914390141364</v>
+        <v>161.3944138396544</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>104.8948334602505</v>
+        <v>90.37478491444013</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.103885330200915</v>
+        <v>4.642684893383167</v>
       </c>
       <c r="C2" t="n">
-        <v>5.260204199354409</v>
+        <v>6.596362824834318</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56637061435917</v>
+        <v>10.16992446829271</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.24730261047896</v>
+        <v>17.53401399784803</v>
       </c>
       <c r="C3" t="n">
-        <v>23.88101290580366</v>
+        <v>9.979465413668827</v>
       </c>
       <c r="D3" t="n">
-        <v>70.51402885752715</v>
+        <v>57.57950285407543</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>47.38797993628929</v>
       </c>
       <c r="C4" t="n">
-        <v>86.36532729029615</v>
+        <v>57.96827494495717</v>
       </c>
       <c r="D4" t="n">
-        <v>147.8305875577805</v>
+        <v>145.4311961686013</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.59588946541137</v>
+        <v>60.57383335202821</v>
       </c>
       <c r="C5" t="n">
-        <v>189.3545884566036</v>
+        <v>168.075206967054</v>
       </c>
       <c r="D5" t="n">
-        <v>131.1860369799801</v>
+        <v>145.1759417654971</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.74976181307086</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>268.7603062714941</v>
+        <v>254.8332333390489</v>
       </c>
       <c r="D6" t="n">
-        <v>69.47435803872979</v>
+        <v>76.67940444019713</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>240.3249657656894</v>
+        <v>227.988324114124</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>42.16017341117502</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>161.806747875438</v>
+        <v>140.8611606053323</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>61.34843229067891</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3131,7 +3131,7 @@
         <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.477530294891449</v>
+        <v>3.313398501832985</v>
       </c>
       <c r="C2" t="n">
-        <v>3.964297229748621</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="D2" t="n">
-        <v>9.19701249338412</v>
+        <v>8.508807352707105</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.2494460323367</v>
+        <v>16.98914402199105</v>
       </c>
       <c r="C3" t="n">
-        <v>22.55074476654924</v>
+        <v>17.59782759862408</v>
       </c>
       <c r="D3" t="n">
-        <v>65.75255249193013</v>
+        <v>53.63778582152449</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.702596865538</v>
+        <v>43.12523140444964</v>
       </c>
       <c r="C4" t="n">
-        <v>77.26550781963248</v>
+        <v>45.20555478974863</v>
       </c>
       <c r="D4" t="n">
-        <v>150.9446912756513</v>
+        <v>142.9807538988012</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.62105505282329</v>
+        <v>66.53795065532759</v>
       </c>
       <c r="C5" t="n">
-        <v>182.5805292973006</v>
+        <v>148.759320885998</v>
       </c>
       <c r="D5" t="n">
-        <v>144.6114368355552</v>
+        <v>159.0431280879833</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.55229165579701</v>
+        <v>58.72716592033996</v>
       </c>
       <c r="C6" t="n">
-        <v>292.9112997959657</v>
+        <v>272.101193709046</v>
       </c>
       <c r="D6" t="n">
-        <v>83.24042434767857</v>
+        <v>91.17000055488006</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="C7" t="n">
-        <v>295.7799665877748</v>
+        <v>282.006046297192</v>
       </c>
       <c r="D7" t="n">
-        <v>44.85507085933252</v>
+        <v>48.02906118716245</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>207.2027617198106</v>
+        <v>185.8399316754</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>78.09999336824222</v>
+        <v>71.77655640518853</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.53330998758427</v>
+        <v>4.323616889502953</v>
       </c>
       <c r="C2" t="n">
-        <v>15.29857447527805</v>
+        <v>8.076838362838508</v>
       </c>
       <c r="D2" t="n">
-        <v>13.44012607113883</v>
+        <v>10.43205110532661</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.775441817634739</v>
+        <v>14.15189315671777</v>
       </c>
       <c r="C3" t="n">
-        <v>19.0999015861217</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="D3" t="n">
-        <v>59.16993413495526</v>
+        <v>48.87140071740622</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="C4" t="n">
-        <v>67.78280674431252</v>
+        <v>44.49084246105696</v>
       </c>
       <c r="D4" t="n">
-        <v>149.2344867748534</v>
+        <v>138.1181575196668</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.13018120069989</v>
+        <v>65.82618356974865</v>
       </c>
       <c r="C5" t="n">
-        <v>165.056332776495</v>
+        <v>120.1413753072034</v>
       </c>
       <c r="D5" t="n">
-        <v>159.7794388661684</v>
+        <v>168.2470128152972</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>70.76241102670161</v>
       </c>
       <c r="C6" t="n">
-        <v>292.9515514518397</v>
+        <v>258.6571406470902</v>
       </c>
       <c r="D6" t="n">
-        <v>101.3536694910322</v>
+        <v>112.7851397592821</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.18852092141116</v>
+        <v>37.06981156465531</v>
       </c>
       <c r="C7" t="n">
-        <v>350.6959879202286</v>
+        <v>328.8373752851734</v>
       </c>
       <c r="D7" t="n">
-        <v>53.65840252331367</v>
+        <v>58.68887775987432</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>277.3829963578938</v>
+        <v>262.6126021475005</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>142.5546753951581</v>
+        <v>130.7953013936898</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>52.67076433284138</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.304382846045517</v>
+        <v>6.482480091141689</v>
       </c>
       <c r="C2" t="n">
-        <v>9.204866475018093</v>
+        <v>7.885397560510381</v>
       </c>
       <c r="D2" t="n">
-        <v>4.924446484502001</v>
+        <v>18.68854929804228</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.55156228333746</v>
+        <v>3.061089341841555</v>
       </c>
       <c r="C2" t="n">
-        <v>8.811185645615122</v>
+        <v>4.522911673465055</v>
       </c>
       <c r="D2" t="n">
-        <v>9.999100367753764</v>
+        <v>7.677267047210058</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.30482481440202</v>
+        <v>18.75628988963531</v>
       </c>
       <c r="C3" t="n">
-        <v>33.63467634749573</v>
+        <v>23.74847696573034</v>
       </c>
       <c r="D3" t="n">
-        <v>64.4222843526757</v>
+        <v>53.82431788533138</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.52690508420682</v>
+        <v>50.8466770983508</v>
       </c>
       <c r="C4" t="n">
-        <v>97.02219861989529</v>
+        <v>66.27680576599792</v>
       </c>
       <c r="D4" t="n">
-        <v>153.1654045826576</v>
+        <v>143.4657372646991</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.06602344255857</v>
+        <v>42.28878236043136</v>
       </c>
       <c r="C5" t="n">
-        <v>247.940382707532</v>
+        <v>201.6755221449011</v>
       </c>
       <c r="D5" t="n">
-        <v>145.3232039211341</v>
+        <v>156.4414966717293</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.86544381125596</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>285.5452467710019</v>
+        <v>269.8068493242212</v>
       </c>
       <c r="D6" t="n">
-        <v>80.38255678061611</v>
+        <v>88.87565617005527</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>195.0506886366435</v>
+        <v>184.690305113727</v>
       </c>
       <c r="D7" t="n">
-        <v>32.57831581772616</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>105.0617305699724</v>
+        <v>96.38308086443061</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.78422079371073</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>40.15937158992001</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.809982913732624</v>
+        <v>8.064075642683301</v>
       </c>
       <c r="C2" t="n">
-        <v>6.264532100798897</v>
+        <v>5.957245069369645</v>
       </c>
       <c r="D2" t="n">
-        <v>24.51620367045135</v>
+        <v>25.37915990248429</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.27046364475338</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C3" t="n">
-        <v>23.1937895128309</v>
+        <v>19.87057353395544</v>
       </c>
       <c r="D3" t="n">
-        <v>7.274750488468865</v>
+        <v>18.83482970597506</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39866615893148</v>
+        <v>13.39633064245836</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1459581261707</v>
+        <v>70.13373101051732</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576313665756645</v>
+        <v>1.576038899112749</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.344233591292136</v>
+        <v>5.923865647425254</v>
       </c>
       <c r="C2" t="n">
-        <v>8.368417430999811</v>
+        <v>5.203262832508095</v>
       </c>
       <c r="D2" t="n">
-        <v>27.16888596732623</v>
+        <v>21.81737923147687</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.55717503212245</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="C3" t="n">
-        <v>23.96446146066464</v>
+        <v>21.97151362104362</v>
       </c>
       <c r="D3" t="n">
-        <v>26.10958019444392</v>
+        <v>35.59817175598934</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.15836448002</v>
+        <v>15.9916883544763</v>
       </c>
       <c r="C4" t="n">
-        <v>35.87600635629119</v>
+        <v>30.83473189498382</v>
       </c>
       <c r="D4" t="n">
-        <v>18.87606310955342</v>
+        <v>24.93835518327748</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44006257775215</v>
+        <v>15.4350212059218</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13929648640672</v>
+        <v>86.11117093830055</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250539490053084</v>
+        <v>3.249478148615115</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.345215338996383</v>
+        <v>5.320090809313465</v>
       </c>
       <c r="C2" t="n">
-        <v>5.566509483079415</v>
+        <v>5.76187727622453</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0386733755599</v>
+        <v>26.99315312826605</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.70796326794897</v>
+        <v>21.25483779694344</v>
       </c>
       <c r="C3" t="n">
-        <v>29.07445826126929</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D3" t="n">
-        <v>41.78318229274425</v>
+        <v>44.79223900626073</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.90457485070559</v>
+        <v>31.30695254072654</v>
       </c>
       <c r="C4" t="n">
-        <v>49.4938287618987</v>
+        <v>44.52913062152258</v>
       </c>
       <c r="D4" t="n">
-        <v>27.70786545695773</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.6337102953247</v>
+        <v>13.8671863224862</v>
       </c>
       <c r="C5" t="n">
-        <v>40.10439371848221</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>31.58773238414113</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5319,7 +5319,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72983725965701</v>
+        <v>16.72273753756845</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0520072839078</v>
+        <v>102.0086989791675</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182459314914253</v>
+        <v>4.180684384392112</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.610287219143022</v>
+        <v>7.045021525675111</v>
       </c>
       <c r="C2" t="n">
-        <v>7.845145904636262</v>
+        <v>7.780350556155972</v>
       </c>
       <c r="D2" t="n">
-        <v>22.35439522569987</v>
+        <v>29.40138024678348</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2219981543468</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74985962406209</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>49.99550183876882</v>
+        <v>55.3411180883927</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>36.32270156172349</v>
       </c>
       <c r="C4" t="n">
-        <v>62.48627787990099</v>
+        <v>48.38347210839555</v>
       </c>
       <c r="D4" t="n">
-        <v>41.61923042613503</v>
+        <v>50.47655821384976</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.73375075016664</v>
+        <v>30.38509144643879</v>
       </c>
       <c r="C5" t="n">
-        <v>67.81422267084844</v>
+        <v>60.42657119639119</v>
       </c>
       <c r="D5" t="n">
-        <v>32.39767424014475</v>
+        <v>37.20823799095412</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>38.7220929509027</v>
+        <v>34.57617239586842</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.40016181936776</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0505145301963</v>
+        <v>18.04002257835893</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7581186017568</v>
+        <v>117.6896711064368</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016838176732098</v>
+        <v>6.013340859452978</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.797801030654163</v>
+        <v>7.152032025438014</v>
       </c>
       <c r="C2" t="n">
-        <v>8.499971623368884</v>
+        <v>10.79038901737669</v>
       </c>
       <c r="D2" t="n">
-        <v>29.19717672430014</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.83282515283756</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="C3" t="n">
-        <v>26.23229865747478</v>
+        <v>24.85785187152924</v>
       </c>
       <c r="D3" t="n">
-        <v>52.557863346853</v>
+        <v>61.50649367106268</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.73942025221387</v>
+        <v>26.75066144531709</v>
       </c>
       <c r="C4" t="n">
-        <v>51.47205038595602</v>
+        <v>43.15075684476006</v>
       </c>
       <c r="D4" t="n">
-        <v>49.27686251926016</v>
+        <v>57.55986789999049</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.65949777754238</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>69.36047530503717</v>
+        <v>55.73872590861267</v>
       </c>
       <c r="D5" t="n">
-        <v>31.857713002809</v>
+        <v>37.3064127613788</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.67298020349458</v>
+        <v>14.53084777055704</v>
       </c>
       <c r="C6" t="n">
-        <v>49.95230493978197</v>
+        <v>44.75984133202059</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>32.32207966691774</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>24.91282974296706</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.05253600279914</v>
+        <v>7.047101551825717</v>
       </c>
       <c r="C21" t="n">
-        <v>66.99909202659182</v>
+        <v>66.0665770483661</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407835001749463</v>
+        <v>4.404438469891073</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.312817664756238</v>
+        <v>5.702972413969722</v>
       </c>
       <c r="C2" t="n">
-        <v>4.979424355939822</v>
+        <v>5.844344083381262</v>
       </c>
       <c r="D2" t="n">
-        <v>21.35693955818511</v>
+        <v>27.63914311766045</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.63433219013045</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C3" t="n">
-        <v>30.7336118814464</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="D3" t="n">
-        <v>64.38301444450582</v>
+        <v>71.34360566761572</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.58099901893164</v>
+        <v>33.92331017254428</v>
       </c>
       <c r="C4" t="n">
-        <v>60.52081897599888</v>
+        <v>55.03284930925921</v>
       </c>
       <c r="D4" t="n">
-        <v>64.91119470939061</v>
+        <v>76.43593100954392</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.5808190924824</v>
+        <v>34.09118902997049</v>
       </c>
       <c r="C5" t="n">
-        <v>85.26478811383549</v>
+        <v>69.72863069412972</v>
       </c>
       <c r="D5" t="n">
-        <v>43.56505437595222</v>
+        <v>49.89732706834415</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.28683456055609</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="C6" t="n">
-        <v>85.45426542075514</v>
+        <v>70.60140440320514</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>12.27675504160636</v>
       </c>
       <c r="C7" t="n">
-        <v>52.46067032413256</v>
+        <v>47.13076203777662</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>27.20422888467911</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272110970718575</v>
+        <v>7.265131937987468</v>
       </c>
       <c r="C21" t="n">
-        <v>76.35716519254505</v>
+        <v>75.37574385661999</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454083228038932</v>
+        <v>5.448848953490601</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.979023445312322</v>
+        <v>5.882632243846888</v>
       </c>
       <c r="C2" t="n">
-        <v>8.968265278294613</v>
+        <v>8.744426801726341</v>
       </c>
       <c r="D2" t="n">
-        <v>21.07517796706628</v>
+        <v>21.47573103039898</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.24654184695297</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="C3" t="n">
-        <v>23.93991776805847</v>
+        <v>27.99944452511903</v>
       </c>
       <c r="D3" t="n">
-        <v>66.5281331782851</v>
+        <v>76.90029767365266</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.06522162130357</v>
+        <v>39.64100880207771</v>
       </c>
       <c r="C4" t="n">
-        <v>69.46748580480005</v>
+        <v>75.09584539324703</v>
       </c>
       <c r="D4" t="n">
-        <v>82.61308756466485</v>
+        <v>95.04397699583795</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.17678100668922</v>
+        <v>43.44233591292137</v>
       </c>
       <c r="C5" t="n">
-        <v>100.5064212222672</v>
+        <v>87.67006998924018</v>
       </c>
       <c r="D5" t="n">
-        <v>56.6222988424348</v>
+        <v>66.07162049581035</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>36.8302651248191</v>
       </c>
       <c r="C6" t="n">
-        <v>113.1876563180233</v>
+        <v>91.77377539299185</v>
       </c>
       <c r="D6" t="n">
-        <v>40.73467574460867</v>
+        <v>44.1560664939088</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="C7" t="n">
-        <v>91.20730696764143</v>
+        <v>77.13395362726339</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>49.81878725200438</v>
+        <v>45.56291095409447</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
         <v>32.9484347022272</v>
@@ -6493,7 +6493,7 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
         <v>33.88011327355743</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.479128608771306</v>
+        <v>7.46966955648754</v>
       </c>
       <c r="C21" t="n">
-        <v>86.00997900087002</v>
+        <v>84.03378251048483</v>
       </c>
       <c r="D21" t="n">
-        <v>6.544237532674893</v>
+        <v>6.535960861926598</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_44_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497624940887</v>
+        <v>10.84497660278321</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907165337321</v>
+        <v>37.78907288469802</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.994952392758523</v>
+        <v>5.293583621298801</v>
       </c>
       <c r="C2" t="n">
-        <v>6.929175296573987</v>
+        <v>10.47033926579223</v>
       </c>
       <c r="D2" t="n">
-        <v>19.27661617288612</v>
+        <v>25.08267209580176</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41053477129119</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="C3" t="n">
-        <v>31.17048960983623</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D3" t="n">
-        <v>75.99708978574559</v>
+        <v>82.2115527536279</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.79416144394021</v>
+        <v>38.35197406640165</v>
       </c>
       <c r="C4" t="n">
-        <v>71.63714823118551</v>
+        <v>68.68895987533233</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2699021410017</v>
+        <v>103.5439486192068</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.5908418581699</v>
+        <v>45.3076565509903</v>
       </c>
       <c r="C5" t="n">
-        <v>114.1527143112979</v>
+        <v>98.29748888771192</v>
       </c>
       <c r="D5" t="n">
-        <v>82.46680715673209</v>
+        <v>70.0722423906161</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.37619896383834</v>
+        <v>40.45291415348983</v>
       </c>
       <c r="C6" t="n">
-        <v>115.7637622939669</v>
+        <v>96.36246416264144</v>
       </c>
       <c r="D6" t="n">
-        <v>54.017722183068</v>
+        <v>46.28940425523712</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.87774886752143</v>
+        <v>28.20659329071511</v>
       </c>
       <c r="C7" t="n">
-        <v>104.2625879387155</v>
+        <v>81.92488242398782</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.94005663677871</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>74.01886816168827</v>
+        <v>55.99398031171682</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.659494467383225</v>
+        <v>7.706213954246745</v>
       </c>
       <c r="C21" t="n">
-        <v>92.87137041702161</v>
+        <v>96.32767442808431</v>
       </c>
       <c r="D21" t="n">
-        <v>7.659494467383225</v>
+        <v>8.669490698527587</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.339545836949155</v>
+        <v>6.686683613625026</v>
       </c>
       <c r="C2" t="n">
-        <v>5.354451978962104</v>
+        <v>11.77508196473624</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12422429454961</v>
+        <v>25.34087174201867</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.90279128174634</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="C3" t="n">
-        <v>28.83883881225006</v>
+        <v>33.34996951326415</v>
       </c>
       <c r="D3" t="n">
-        <v>73.66053024963819</v>
+        <v>82.56007318863551</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.76038111136832</v>
+        <v>36.08020987877453</v>
       </c>
       <c r="C4" t="n">
-        <v>74.55981114672825</v>
+        <v>66.08536496366979</v>
       </c>
       <c r="D4" t="n">
-        <v>121.1565024333946</v>
+        <v>117.3787372674529</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.97787143782139</v>
+        <v>50.87907477259096</v>
       </c>
       <c r="C5" t="n">
-        <v>121.3194725522996</v>
+        <v>111.1829275059513</v>
       </c>
       <c r="D5" t="n">
-        <v>99.05834335850319</v>
+        <v>88.99542938997337</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>50.636583089642</v>
       </c>
       <c r="C6" t="n">
-        <v>146.1940141348011</v>
+        <v>125.2631530802591</v>
       </c>
       <c r="D6" t="n">
-        <v>65.73095404243671</v>
+        <v>55.74854338565514</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.83699849002857</v>
+        <v>37.54890444432775</v>
       </c>
       <c r="C7" t="n">
-        <v>132.4691812294306</v>
+        <v>108.7540836856447</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>43.17824578047897</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.11801501315464</v>
+        <v>21.94696992843745</v>
       </c>
       <c r="C8" t="n">
-        <v>103.9768993567797</v>
+        <v>81.61268665403733</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>64.23280704575605</v>
+        <v>51.69687061022852</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.834132639644568</v>
+        <v>7.89082593166062</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8644577354238</v>
+        <v>105.5397968359608</v>
       </c>
       <c r="D21" t="n">
-        <v>8.813399219600139</v>
+        <v>9.863532414575776</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.49506288484765</v>
+        <v>7.699847244407733</v>
       </c>
       <c r="C2" t="n">
-        <v>5.238605749860979</v>
+        <v>15.44583663091507</v>
       </c>
       <c r="D2" t="n">
-        <v>20.78752588972196</v>
+        <v>27.75302585135308</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61455836732528</v>
+        <v>19.68895020866978</v>
       </c>
       <c r="C3" t="n">
-        <v>25.13764996723958</v>
+        <v>39.42207906403067</v>
       </c>
       <c r="D3" t="n">
-        <v>69.77771807934205</v>
+        <v>82.79078389913353</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.07944911524854</v>
+        <v>34.75288698263284</v>
       </c>
       <c r="C4" t="n">
-        <v>72.46672504127406</v>
+        <v>73.18143736996574</v>
       </c>
       <c r="D4" t="n">
-        <v>126.440268577651</v>
+        <v>128.7503209257437</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.86144437164352</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="C5" t="n">
-        <v>126.7190849256571</v>
+        <v>114.6681318560275</v>
       </c>
       <c r="D5" t="n">
-        <v>115.3308115563941</v>
+        <v>105.1206354322272</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.08063615159783</v>
+        <v>58.16364273810229</v>
       </c>
       <c r="C6" t="n">
-        <v>166.1588354483642</v>
+        <v>148.206596928507</v>
       </c>
       <c r="D6" t="n">
-        <v>77.20267596656069</v>
+        <v>67.98504677138737</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.25726862290422</v>
+        <v>47.25053525769474</v>
       </c>
       <c r="C7" t="n">
-        <v>164.4486309475662</v>
+        <v>139.5358012045992</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4007837141735</v>
+        <v>47.72962813736718</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.04701038327938</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="C8" t="n">
-        <v>133.6845848872882</v>
+        <v>108.8169155387164</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.19531103988288</v>
+        <v>15.8640611529242</v>
       </c>
       <c r="C9" t="n">
-        <v>91.74530470956864</v>
+        <v>73.88436872620643</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>54.23665192111504</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>37.6716229073586</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.993800603895563</v>
+        <v>8.059754833581435</v>
       </c>
       <c r="C21" t="n">
-        <v>108.915533228077</v>
+        <v>113.8440370243378</v>
       </c>
       <c r="D21" t="n">
-        <v>9.992250754869454</v>
+        <v>11.08216289617447</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.806857744170636</v>
+        <v>7.007715112913733</v>
       </c>
       <c r="C2" t="n">
-        <v>3.603995822290041</v>
+        <v>10.37903672929728</v>
       </c>
       <c r="D2" t="n">
-        <v>17.29937629653305</v>
+        <v>22.8374150961893</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.06187546756333</v>
+        <v>23.96937019918587</v>
       </c>
       <c r="C3" t="n">
-        <v>38.56795856133595</v>
+        <v>59.07666810305182</v>
       </c>
       <c r="D3" t="n">
-        <v>78.57417750939346</v>
+        <v>91.0325558762855</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.84000048640355</v>
+        <v>24.96388062358789</v>
       </c>
       <c r="C4" t="n">
-        <v>102.9058126114464</v>
+        <v>97.97940263153592</v>
       </c>
       <c r="D4" t="n">
-        <v>123.9898263078509</v>
+        <v>122.5348762101572</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.10377182367646</v>
+        <v>32.7658296292373</v>
       </c>
       <c r="C5" t="n">
-        <v>99.27923659195872</v>
+        <v>88.55364292306231</v>
       </c>
       <c r="D5" t="n">
-        <v>77.11628216858696</v>
+        <v>69.87589284976674</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.6906359666378</v>
+        <v>29.34345713223292</v>
       </c>
       <c r="C6" t="n">
-        <v>108.3172059572549</v>
+        <v>91.89453036061421</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>31.43654323768712</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="C7" t="n">
-        <v>93.96209102575797</v>
+        <v>76.47520091771378</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>67.59332943739288</v>
+        <v>54.40845776935822</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.840016181936775</v>
+        <v>4.356996311447345</v>
       </c>
       <c r="C2" t="n">
-        <v>1.867284133477433</v>
+        <v>5.19246360776138</v>
       </c>
       <c r="D2" t="n">
-        <v>11.93314334511998</v>
+        <v>17.2061102646296</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.70492021384499</v>
+        <v>24.76458583962579</v>
       </c>
       <c r="C3" t="n">
-        <v>26.60045404656733</v>
+        <v>50.51091938349839</v>
       </c>
       <c r="D3" t="n">
-        <v>75.87928006123597</v>
+        <v>88.93652452771856</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.52239725631309</v>
+        <v>34.52315801983909</v>
       </c>
       <c r="C4" t="n">
-        <v>102.510168286635</v>
+        <v>125.8659461706666</v>
       </c>
       <c r="D4" t="n">
-        <v>132.9620185769625</v>
+        <v>138.6924799266511</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.00621894805753</v>
+        <v>36.25103397931348</v>
       </c>
       <c r="C5" t="n">
-        <v>142.6724851196678</v>
+        <v>131.3332991356171</v>
       </c>
       <c r="D5" t="n">
-        <v>96.38308086443064</v>
+        <v>89.78082755337083</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>133.7562524696982</v>
+        <v>116.4077887879528</v>
       </c>
       <c r="D6" t="n">
-        <v>43.91455655866408</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>119.0545805986022</v>
+        <v>99.71120558182729</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>88.45546815263761</v>
+        <v>70.76437452211009</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.78347572571796</v>
+        <v>5.657812019574368</v>
       </c>
       <c r="C2" t="n">
-        <v>2.819579406596839</v>
+        <v>12.95612445294516</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06626012227005</v>
+        <v>17.60077284173682</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.25131171675396</v>
+        <v>19.72822011683965</v>
       </c>
       <c r="C3" t="n">
-        <v>16.39518666092173</v>
+        <v>34.55751918948773</v>
       </c>
       <c r="D3" t="n">
-        <v>68.57507714163971</v>
+        <v>83.25220532012952</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.65675782307466</v>
+        <v>40.98109441837461</v>
       </c>
       <c r="C4" t="n">
-        <v>84.0425122220482</v>
+        <v>125.9169970512874</v>
       </c>
       <c r="D4" t="n">
-        <v>139.4071922553428</v>
+        <v>149.579080219044</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.61476365597031</v>
+        <v>43.4914232981337</v>
       </c>
       <c r="C5" t="n">
-        <v>165.3017697025567</v>
+        <v>180.6661212740193</v>
       </c>
       <c r="D5" t="n">
-        <v>117.9078992800419</v>
+        <v>114.2263453891164</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.77242412572655</v>
+        <v>41.66046382971341</v>
       </c>
       <c r="C6" t="n">
-        <v>178.9588620163341</v>
+        <v>161.046875152351</v>
       </c>
       <c r="D6" t="n">
-        <v>59.73345731719294</v>
+        <v>54.82275530055039</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.38058361854505</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="C7" t="n">
-        <v>154.6272269142811</v>
+        <v>131.3313356402086</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>120.3328161095315</v>
+        <v>99.47067739428682</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -2436,10 +2436,10 @@
         <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>73.1078062921472</v>
+        <v>62.34686970589792</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.435135217159589</v>
+        <v>3.334015203622168</v>
       </c>
       <c r="C2" t="n">
-        <v>1.334195130071415</v>
+        <v>6.030876147188157</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7410806479861</v>
+        <v>12.27577329390212</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.01216618754523</v>
+        <v>21.01430960940298</v>
       </c>
       <c r="C3" t="n">
-        <v>15.12382338392211</v>
+        <v>43.65832040785565</v>
       </c>
       <c r="D3" t="n">
-        <v>65.65928646002668</v>
+        <v>81.877758534184</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.51935420220912</v>
+        <v>45.20555478974863</v>
       </c>
       <c r="C4" t="n">
-        <v>76.8443380545106</v>
+        <v>123.6069447031947</v>
       </c>
       <c r="D4" t="n">
-        <v>145.8013150531023</v>
+        <v>158.5512724881556</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.94641445355649</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="C5" t="n">
-        <v>188.6428213710246</v>
+        <v>221.6786316189298</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7002107350981</v>
+        <v>120.4358996184775</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.48058301565798</v>
+        <v>34.45541742824607</v>
       </c>
       <c r="C6" t="n">
-        <v>214.7828357443002</v>
+        <v>190.2293256610875</v>
       </c>
       <c r="D6" t="n">
-        <v>58.00263611460582</v>
+        <v>53.53470231257858</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>161.3944138396544</v>
+        <v>135.7629447771787</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>90.37478491444013</v>
+        <v>76.10508203321274</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.642684893383167</v>
+        <v>3.527419501358789</v>
       </c>
       <c r="C2" t="n">
-        <v>6.596362824834318</v>
+        <v>6.066219064541041</v>
       </c>
       <c r="D2" t="n">
-        <v>10.16992446829271</v>
+        <v>15.88762309782613</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.53401399784803</v>
+        <v>16.38536918387927</v>
       </c>
       <c r="C3" t="n">
-        <v>9.979465413668827</v>
+        <v>33.43341806812513</v>
       </c>
       <c r="D3" t="n">
-        <v>57.57950285407543</v>
+        <v>74.37229733521711</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.38797993628929</v>
+        <v>43.18904500522568</v>
       </c>
       <c r="C4" t="n">
-        <v>57.96827494495717</v>
+        <v>117.4680763085394</v>
       </c>
       <c r="D4" t="n">
-        <v>145.4311961686013</v>
+        <v>162.0737832509932</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.57383335202821</v>
+        <v>54.78152189697203</v>
       </c>
       <c r="C5" t="n">
-        <v>168.075206967054</v>
+        <v>226.2683021362837</v>
       </c>
       <c r="D5" t="n">
-        <v>145.1759417654971</v>
+        <v>143.3351648200344</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.15356321915257</v>
+        <v>44.47807974090175</v>
       </c>
       <c r="C6" t="n">
-        <v>254.8332333390489</v>
+        <v>261.9175247728938</v>
       </c>
       <c r="D6" t="n">
-        <v>76.67940444019713</v>
+        <v>72.17121898229578</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>227.988324114124</v>
+        <v>196.0687610059475</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>140.8611606053323</v>
+        <v>117.4121166893973</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>61.34843229067891</v>
+        <v>53.47187045950676</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.313398501832985</v>
+        <v>2.415099352447153</v>
       </c>
       <c r="C2" t="n">
-        <v>3.994731408580272</v>
+        <v>3.277073836775853</v>
       </c>
       <c r="D2" t="n">
-        <v>8.508807352707105</v>
+        <v>11.76919147851076</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98914402199105</v>
+        <v>14.70658060961722</v>
       </c>
       <c r="C3" t="n">
-        <v>17.59782759862408</v>
+        <v>29.6095107600838</v>
       </c>
       <c r="D3" t="n">
-        <v>53.63778582152449</v>
+        <v>71.64794745593223</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.12523140444964</v>
+        <v>39.21983903695583</v>
       </c>
       <c r="C4" t="n">
-        <v>45.20555478974863</v>
+        <v>105.2541531200048</v>
       </c>
       <c r="D4" t="n">
-        <v>142.9807538988012</v>
+        <v>162.5970547773567</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.53795065532759</v>
+        <v>60.10750319251098</v>
       </c>
       <c r="C5" t="n">
-        <v>148.759320885998</v>
+        <v>230.0971181828462</v>
       </c>
       <c r="D5" t="n">
-        <v>159.0431280879833</v>
+        <v>158.1104677689488</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.72716592033996</v>
+        <v>52.1258943569844</v>
       </c>
       <c r="C6" t="n">
-        <v>272.101193709046</v>
+        <v>305.4698164286908</v>
       </c>
       <c r="D6" t="n">
-        <v>91.17000055488006</v>
+        <v>87.46684821446109</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.00212772632452</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>282.006046297192</v>
+        <v>254.937298595699</v>
       </c>
       <c r="D7" t="n">
-        <v>48.02906118716245</v>
+        <v>45.27427712904591</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>185.8399316754</v>
+        <v>152.5439582858694</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>61.12655730951914</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.323616889502953</v>
+        <v>4.828235209485814</v>
       </c>
       <c r="C2" t="n">
-        <v>8.076838362838508</v>
+        <v>9.5111717587431</v>
       </c>
       <c r="D2" t="n">
-        <v>10.43205110532661</v>
+        <v>23.57078063126167</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.15189315671777</v>
+        <v>11.618984079761</v>
       </c>
       <c r="C3" t="n">
-        <v>16.64062358698343</v>
+        <v>21.83406894244906</v>
       </c>
       <c r="D3" t="n">
-        <v>48.87140071740622</v>
+        <v>66.21397391292612</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.17329598422873</v>
+        <v>34.11475097487241</v>
       </c>
       <c r="C4" t="n">
-        <v>44.49084246105696</v>
+        <v>91.39383903144832</v>
       </c>
       <c r="D4" t="n">
-        <v>138.1181575196668</v>
+        <v>159.2659848168473</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.82618356974865</v>
+        <v>59.42027979953821</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1413753072034</v>
+        <v>214.4136986075034</v>
       </c>
       <c r="D5" t="n">
-        <v>168.2470128152972</v>
+        <v>174.0638679629595</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.76241102670161</v>
+        <v>62.47056991663305</v>
       </c>
       <c r="C6" t="n">
-        <v>258.6571406470902</v>
+        <v>329.8623198884071</v>
       </c>
       <c r="D6" t="n">
-        <v>112.7851397592821</v>
+        <v>107.7536827750172</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.06981156465531</v>
+        <v>31.32069700858599</v>
       </c>
       <c r="C7" t="n">
-        <v>328.8373752851734</v>
+        <v>327.1605502063198</v>
       </c>
       <c r="D7" t="n">
-        <v>58.68887775987432</v>
+        <v>54.73636150257666</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>262.6126021475005</v>
+        <v>223.4752299177015</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>130.7953013936898</v>
+        <v>106.0562409943744</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.482480091141689</v>
+        <v>4.956844158742146</v>
       </c>
       <c r="C2" t="n">
-        <v>7.885397560510381</v>
+        <v>4.52782041198629</v>
       </c>
       <c r="D2" t="n">
-        <v>18.68854929804228</v>
+        <v>7.322856125976958</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.061089341841555</v>
+        <v>3.526437753654543</v>
       </c>
       <c r="C2" t="n">
-        <v>4.522911673465055</v>
+        <v>5.554728510628453</v>
       </c>
       <c r="D2" t="n">
-        <v>7.677267047210058</v>
+        <v>17.53597749325652</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75628988963531</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="C3" t="n">
-        <v>23.74847696573034</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="D3" t="n">
-        <v>53.82431788533138</v>
+        <v>74.86807992586175</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.8466770983508</v>
+        <v>45.98408071921636</v>
       </c>
       <c r="C4" t="n">
-        <v>66.27680576599792</v>
+        <v>129.0311007691583</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4657372646991</v>
+        <v>162.3800885347182</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.28878236043136</v>
+        <v>35.7356164345839</v>
       </c>
       <c r="C5" t="n">
-        <v>201.6755221449011</v>
+        <v>297.4695543867836</v>
       </c>
       <c r="D5" t="n">
-        <v>156.4414966717293</v>
+        <v>158.1595551541612</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>19.44154978719959</v>
       </c>
       <c r="C6" t="n">
-        <v>269.8068493242212</v>
+        <v>273.6710082881366</v>
       </c>
       <c r="D6" t="n">
-        <v>88.87565617005527</v>
+        <v>83.07941772418209</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.707300315414209</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>184.690305113727</v>
+        <v>157.1424645325614</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>96.38308086443061</v>
+        <v>78.10784734987622</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.23494080095125</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.064075642683301</v>
+        <v>6.479534848028949</v>
       </c>
       <c r="C2" t="n">
-        <v>5.957245069369645</v>
+        <v>4.757549374780043</v>
       </c>
       <c r="D2" t="n">
-        <v>25.37915990248429</v>
+        <v>12.96790542539612</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76901155206151</v>
+        <v>10.53415286656828</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87057353395544</v>
+        <v>11.5895316486336</v>
       </c>
       <c r="D3" t="n">
-        <v>18.83482970597506</v>
+        <v>9.58185759344887</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39633064245836</v>
+        <v>13.39911796873997</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13373101051732</v>
+        <v>70.14832348340339</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576038899112749</v>
+        <v>1.576366819851761</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.923865647425254</v>
+        <v>4.12726734865359</v>
       </c>
       <c r="C2" t="n">
-        <v>5.203262832508095</v>
+        <v>3.987859174650544</v>
       </c>
       <c r="D2" t="n">
-        <v>21.81737923147687</v>
+        <v>18.60215550006856</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.19731559302038</v>
+        <v>17.61255381418778</v>
       </c>
       <c r="C3" t="n">
-        <v>21.97151362104362</v>
+        <v>16.02212253330795</v>
       </c>
       <c r="D3" t="n">
-        <v>35.59817175598934</v>
+        <v>18.15742379004476</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.9916883544763</v>
+        <v>12.32878766993144</v>
       </c>
       <c r="C4" t="n">
-        <v>30.83473189498382</v>
+        <v>18.49318150489717</v>
       </c>
       <c r="D4" t="n">
-        <v>24.93835518327748</v>
+        <v>20.08852152429823</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4350212059218</v>
+        <v>15.44484297386989</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11117093830055</v>
+        <v>86.16596606474783</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249478148615115</v>
+        <v>3.251545889235767</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.320090809313465</v>
+        <v>5.43888228152733</v>
       </c>
       <c r="C2" t="n">
-        <v>5.76187727622453</v>
+        <v>5.937610115284709</v>
       </c>
       <c r="D2" t="n">
-        <v>26.99315312826605</v>
+        <v>30.07682266730528</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.25483779694344</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C3" t="n">
-        <v>20.92595231602077</v>
+        <v>15.7128720064702</v>
       </c>
       <c r="D3" t="n">
-        <v>44.79223900626073</v>
+        <v>28.82411259668635</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.30695254072654</v>
+        <v>24.56823629877643</v>
       </c>
       <c r="C4" t="n">
-        <v>44.52913062152258</v>
+        <v>31.03893541746715</v>
       </c>
       <c r="D4" t="n">
-        <v>37.15227837181205</v>
+        <v>24.68310078017331</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.8671863224862</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C5" t="n">
-        <v>34.82749980815561</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>29.67332436085985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72273753756845</v>
+        <v>16.74359993623748</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0086989791675</v>
+        <v>102.1359596110486</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180684384392112</v>
+        <v>5.023079980871243</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.045021525675111</v>
+        <v>5.436918786118836</v>
       </c>
       <c r="C2" t="n">
-        <v>7.780350556155972</v>
+        <v>5.838453597155781</v>
       </c>
       <c r="D2" t="n">
-        <v>29.40138024678348</v>
+        <v>33.5816619714664</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.56623174563893</v>
+        <v>17.40638679629595</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71135047941821</v>
+        <v>20.0227444281137</v>
       </c>
       <c r="D3" t="n">
-        <v>55.3411180883927</v>
+        <v>45.26838664282042</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.32270156172349</v>
+        <v>27.86101809882023</v>
       </c>
       <c r="C4" t="n">
-        <v>48.38347210839555</v>
+        <v>35.76114187489431</v>
       </c>
       <c r="D4" t="n">
-        <v>50.47655821384976</v>
+        <v>32.85124167950677</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.38509144643879</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>60.42657119639119</v>
+        <v>41.45429681182157</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20823799095412</v>
+        <v>32.00497515844602</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>34.57617239586842</v>
+        <v>24.11074186859742</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.40016181936776</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04002257835893</v>
+        <v>18.07600744360855</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6896711064368</v>
+        <v>117.9244295130653</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013340859452978</v>
+        <v>6.886098073755636</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.152032025438014</v>
+        <v>6.698464586075987</v>
       </c>
       <c r="C2" t="n">
-        <v>10.79038901737669</v>
+        <v>9.309913479372502</v>
       </c>
       <c r="D2" t="n">
-        <v>29.40432548989622</v>
+        <v>35.48723426540946</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.56623174563893</v>
+        <v>16.19392838155114</v>
       </c>
       <c r="C3" t="n">
-        <v>24.85785187152924</v>
+        <v>20.29763378530281</v>
       </c>
       <c r="D3" t="n">
-        <v>61.50649367106268</v>
+        <v>57.12299017160066</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.75066144531709</v>
+        <v>22.83250635766807</v>
       </c>
       <c r="C4" t="n">
-        <v>43.15075684476006</v>
+        <v>36.82044764777662</v>
       </c>
       <c r="D4" t="n">
-        <v>57.55986789999049</v>
+        <v>41.04490801915065</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.84450831429729</v>
+        <v>20.29763378530281</v>
       </c>
       <c r="C5" t="n">
-        <v>55.73872590861267</v>
+        <v>40.54618018539328</v>
       </c>
       <c r="D5" t="n">
-        <v>37.3064127613788</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.53084777055704</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>44.75984133202059</v>
+        <v>31.43654323768712</v>
       </c>
       <c r="D6" t="n">
-        <v>32.32207966691774</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>22.63713856452295</v>
+        <v>18.26541603751191</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.047101551825717</v>
+        <v>7.06750117283307</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0665770483661</v>
+        <v>67.14126114191416</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404438469891073</v>
+        <v>5.300625879624802</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.702972413969722</v>
+        <v>6.262568605390403</v>
       </c>
       <c r="C2" t="n">
-        <v>5.844344083381262</v>
+        <v>7.250206795862695</v>
       </c>
       <c r="D2" t="n">
-        <v>27.63914311766045</v>
+        <v>25.70510014029423</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.87472150895069</v>
+        <v>20.6854241284803</v>
       </c>
       <c r="C3" t="n">
-        <v>35.82397372796611</v>
+        <v>30.84651286743478</v>
       </c>
       <c r="D3" t="n">
-        <v>71.34360566761572</v>
+        <v>73.99923320760334</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.92331017254428</v>
+        <v>28.34600146471816</v>
       </c>
       <c r="C4" t="n">
-        <v>55.03284930925921</v>
+        <v>45.84369079750906</v>
       </c>
       <c r="D4" t="n">
-        <v>76.43593100954392</v>
+        <v>62.48627787990099</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.09118902997049</v>
+        <v>28.81429511964389</v>
       </c>
       <c r="C5" t="n">
-        <v>69.72863069412972</v>
+        <v>57.70222131710629</v>
       </c>
       <c r="D5" t="n">
-        <v>49.89732706834415</v>
+        <v>38.75449062514284</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.28433128579986</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="C6" t="n">
-        <v>70.60140440320514</v>
+        <v>51.24035792775378</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>47.13076203777662</v>
+        <v>34.43480072645687</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>25.53525778745954</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.265131937987468</v>
+        <v>7.293062744257213</v>
       </c>
       <c r="C21" t="n">
-        <v>75.37574385661999</v>
+        <v>77.48879165773289</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448848953490601</v>
+        <v>6.381429901225061</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.882632243846888</v>
+        <v>4.480696522182442</v>
       </c>
       <c r="C2" t="n">
-        <v>8.744426801726341</v>
+        <v>5.847289326494002</v>
       </c>
       <c r="D2" t="n">
-        <v>21.47573103039898</v>
+        <v>28.99199145411256</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08303194870025</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="C3" t="n">
-        <v>27.99944452511903</v>
+        <v>29.24135537099124</v>
       </c>
       <c r="D3" t="n">
-        <v>76.90029767365266</v>
+        <v>77.39117152577607</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.64100880207771</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>75.09584539324703</v>
+        <v>64.66870302644165</v>
       </c>
       <c r="D4" t="n">
-        <v>95.04397699583795</v>
+        <v>84.92313991275759</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.44233591292137</v>
+        <v>36.3982961349505</v>
       </c>
       <c r="C5" t="n">
-        <v>87.67006998924018</v>
+        <v>73.45927197026759</v>
       </c>
       <c r="D5" t="n">
-        <v>66.07162049581035</v>
+        <v>53.18618187757097</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.8302651248191</v>
+        <v>31.23528495831652</v>
       </c>
       <c r="C6" t="n">
-        <v>91.77377539299185</v>
+        <v>73.94229184075704</v>
       </c>
       <c r="D6" t="n">
-        <v>44.1560664939088</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>77.13395362726339</v>
+        <v>56.17364014159399</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>45.56291095409447</v>
+        <v>35.46563581591602</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.46966955648754</v>
+        <v>7.506700070815319</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03378251048483</v>
+        <v>87.26538832322808</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535960861926598</v>
+        <v>7.506700070815319</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_44_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497660278321</v>
+        <v>10.84497654876275</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907288469802</v>
+        <v>37.78907269646498</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.293583621298801</v>
+        <v>1.001382658331747</v>
       </c>
       <c r="C2" t="n">
-        <v>10.47033926579223</v>
+        <v>3.962333734340127</v>
       </c>
       <c r="D2" t="n">
-        <v>25.08267209580176</v>
+        <v>13.84067913447153</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.05924901962008</v>
+        <v>10.4507043117073</v>
       </c>
       <c r="C3" t="n">
-        <v>25.49598787928967</v>
+        <v>38.57286729985718</v>
       </c>
       <c r="D3" t="n">
-        <v>82.2115527536279</v>
+        <v>62.22316949516284</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.35197406640165</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="C4" t="n">
-        <v>68.68895987533233</v>
+        <v>101.5784897153047</v>
       </c>
       <c r="D4" t="n">
-        <v>103.5439486192068</v>
+        <v>66.14917856444583</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>17.20512851692536</v>
       </c>
       <c r="C5" t="n">
-        <v>98.29748888771192</v>
+        <v>96.43216824964297</v>
       </c>
       <c r="D5" t="n">
-        <v>70.0722423906161</v>
+        <v>42.01880174176349</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.45291415348983</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>96.36246416264144</v>
+        <v>53.09193409796327</v>
       </c>
       <c r="D6" t="n">
-        <v>46.28940425523712</v>
+        <v>29.7057220351</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.20659329071511</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>81.92488242398782</v>
+        <v>34.7941203862112</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>55.99398031171682</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
+        <v>32.39374724932775</v>
+      </c>
+      <c r="D9" t="n">
         <v>35.83280945730432</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>25.02769422436394</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.706213954246745</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.32767442808431</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.669490698527587</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.686683613625026</v>
+        <v>1.607120991852028</v>
       </c>
       <c r="C2" t="n">
-        <v>11.77508196473624</v>
+        <v>4.883213080923635</v>
       </c>
       <c r="D2" t="n">
-        <v>25.34087174201867</v>
+        <v>19.26287170502667</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81381209355838</v>
+        <v>6.680793127399546</v>
       </c>
       <c r="C3" t="n">
-        <v>33.34996951326415</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>82.56007318863551</v>
+        <v>58.85577486959628</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.08020987877453</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C4" t="n">
-        <v>66.08536496366979</v>
+        <v>98.74516584084844</v>
       </c>
       <c r="D4" t="n">
-        <v>117.3787372674529</v>
+        <v>82.49822308326797</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.87907477259096</v>
+        <v>22.97289627937537</v>
       </c>
       <c r="C5" t="n">
-        <v>111.1829275059513</v>
+        <v>148.5138839599363</v>
       </c>
       <c r="D5" t="n">
-        <v>88.99542938997337</v>
+        <v>56.27868714594842</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.636583089642</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="C6" t="n">
-        <v>125.2631530802591</v>
+        <v>106.4656297870454</v>
       </c>
       <c r="D6" t="n">
-        <v>55.74854338565514</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.54890444432775</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>108.7540836856447</v>
+        <v>56.77250624118454</v>
       </c>
       <c r="D7" t="n">
-        <v>43.17824578047897</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.94696992843745</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>81.61268665403733</v>
+        <v>37.96909246174539</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>51.69687061022852</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>27.38879745307752</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.89082593166062</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.5397968359608</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.863532414575776</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.699847244407733</v>
+        <v>0.8443030256522569</v>
       </c>
       <c r="C2" t="n">
-        <v>15.44583663091507</v>
+        <v>1.975276380944582</v>
       </c>
       <c r="D2" t="n">
-        <v>27.75302585135308</v>
+        <v>12.95416095753666</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.68895020866978</v>
+        <v>6.803511590430396</v>
       </c>
       <c r="C3" t="n">
-        <v>39.42207906403067</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D3" t="n">
-        <v>82.79078389913353</v>
+        <v>62.04645490839842</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.75288698263284</v>
+        <v>21.44136986075034</v>
       </c>
       <c r="C4" t="n">
-        <v>73.18143736996574</v>
+        <v>93.39758609581605</v>
       </c>
       <c r="D4" t="n">
-        <v>128.7503209257437</v>
+        <v>92.07026319967437</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.95899724726245</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="C5" t="n">
-        <v>114.6681318560275</v>
+        <v>176.8863926126691</v>
       </c>
       <c r="D5" t="n">
-        <v>105.1206354322272</v>
+        <v>65.11441648416971</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.16364273810229</v>
+        <v>14.24908617943821</v>
       </c>
       <c r="C6" t="n">
-        <v>148.206596928507</v>
+        <v>144.4229412763398</v>
       </c>
       <c r="D6" t="n">
-        <v>67.98504677138737</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.25053525769474</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>139.5358012045992</v>
+        <v>57.97023844036566</v>
       </c>
       <c r="D7" t="n">
-        <v>47.72962813736718</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.95803119509142</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>108.8169155387164</v>
+        <v>39.80496066868692</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.8640611529242</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>73.88436872620643</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.059754833581435</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.8440370243378</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08216289617447</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.007715112913733</v>
+        <v>1.036725575684632</v>
       </c>
       <c r="C2" t="n">
-        <v>10.37903672929728</v>
+        <v>8.760134764994289</v>
       </c>
       <c r="D2" t="n">
-        <v>22.8374150961893</v>
+        <v>15.58720830032661</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.96937019918587</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C3" t="n">
-        <v>59.07666810305182</v>
+        <v>14.48077863764045</v>
       </c>
       <c r="D3" t="n">
-        <v>91.0325558762855</v>
+        <v>58.09001166028377</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.96388062358789</v>
+        <v>17.54874021341173</v>
       </c>
       <c r="C4" t="n">
-        <v>97.97940263153592</v>
+        <v>75.15965899402306</v>
       </c>
       <c r="D4" t="n">
-        <v>122.5348762101572</v>
+        <v>101.8975577191849</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.7658296292373</v>
+        <v>27.88163480060942</v>
       </c>
       <c r="C5" t="n">
-        <v>88.55364292306231</v>
+        <v>176.2728002975148</v>
       </c>
       <c r="D5" t="n">
-        <v>69.87589284976674</v>
+        <v>83.08039947188634</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.34345713223292</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>91.89453036061421</v>
+        <v>215.6683721735308</v>
       </c>
       <c r="D6" t="n">
-        <v>31.43654323768712</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>76.47520091771378</v>
+        <v>129.7742837812731</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>54.40845776935822</v>
+        <v>57.41260574435346</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.356996311447345</v>
+        <v>0.5429064804484861</v>
       </c>
       <c r="C2" t="n">
-        <v>5.19246360776138</v>
+        <v>3.940735284846697</v>
       </c>
       <c r="D2" t="n">
-        <v>17.2061102646296</v>
+        <v>11.65334524940964</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.76458583962579</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C3" t="n">
-        <v>50.51091938349839</v>
+        <v>25.30945581548277</v>
       </c>
       <c r="D3" t="n">
-        <v>88.93652452771856</v>
+        <v>57.44205817548087</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>14.56226369709294</v>
       </c>
       <c r="C4" t="n">
-        <v>125.8659461706666</v>
+        <v>58.10866486666446</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6924799266511</v>
+        <v>107.3217137851486</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.25103397931348</v>
+        <v>29.15790681613028</v>
       </c>
       <c r="C5" t="n">
-        <v>131.3332991356171</v>
+        <v>165.9644494029233</v>
       </c>
       <c r="D5" t="n">
-        <v>89.78082755337083</v>
+        <v>97.31574118346511</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>26.80760281216341</v>
       </c>
       <c r="C6" t="n">
-        <v>116.4077887879528</v>
+        <v>251.2910876221264</v>
       </c>
       <c r="D6" t="n">
-        <v>39.92964262712628</v>
+        <v>57.11709968537519</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>99.71120558182729</v>
+        <v>196.667627105538</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>40.66300816219864</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>70.76437452211009</v>
+        <v>89.62374792069132</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
+        <v>48.03593342109217</v>
+      </c>
+      <c r="D9" t="n">
         <v>41.60155896745857</v>
-      </c>
-      <c r="D9" t="n">
-        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.657812019574368</v>
+        <v>0.735329030480861</v>
       </c>
       <c r="C2" t="n">
-        <v>12.95612445294516</v>
+        <v>4.618141200776996</v>
       </c>
       <c r="D2" t="n">
-        <v>17.60077284173682</v>
+        <v>11.34802171338888</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.72822011683965</v>
+        <v>3.058144098728814</v>
       </c>
       <c r="C3" t="n">
-        <v>34.55751918948773</v>
+        <v>20.10128424445344</v>
       </c>
       <c r="D3" t="n">
-        <v>83.25220532012952</v>
+        <v>53.69178194525806</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.98109441837461</v>
+        <v>11.56302446061893</v>
       </c>
       <c r="C4" t="n">
-        <v>125.9169970512874</v>
+        <v>60.66120889770617</v>
       </c>
       <c r="D4" t="n">
-        <v>149.579080219044</v>
+        <v>110.9080381487622</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.4914232981337</v>
+        <v>26.53173170727006</v>
       </c>
       <c r="C5" t="n">
-        <v>180.6661212740193</v>
+        <v>138.5982321470435</v>
       </c>
       <c r="D5" t="n">
-        <v>114.2263453891164</v>
+        <v>111.1092964281328</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.66046382971341</v>
+        <v>32.48308629041422</v>
       </c>
       <c r="C6" t="n">
-        <v>161.046875152351</v>
+        <v>258.0936174648525</v>
       </c>
       <c r="D6" t="n">
-        <v>54.82275530055039</v>
+        <v>71.08442427369457</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.26647990067416</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>131.3313356402086</v>
+        <v>274.8795397120644</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>46.29234949834984</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>99.47067739428682</v>
+        <v>164.5605501858504</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>42.14152020479433</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>62.34686970589792</v>
+        <v>74.88280614142545</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.59999638267758</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
+        <v>33.05151821117311</v>
+      </c>
+      <c r="D11" t="n">
         <v>33.22921454564179</v>
-      </c>
-      <c r="D11" t="n">
-        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.15820991576653</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.334015203622168</v>
+        <v>0.4879286090106648</v>
       </c>
       <c r="C2" t="n">
-        <v>6.030876147188157</v>
+        <v>2.401354884587698</v>
       </c>
       <c r="D2" t="n">
-        <v>12.27577329390212</v>
+        <v>8.171086142446203</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.01430960940298</v>
+        <v>4.314781160164731</v>
       </c>
       <c r="C3" t="n">
-        <v>43.65832040785565</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="D3" t="n">
-        <v>81.877758534184</v>
+        <v>57.61386402372407</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.20555478974863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="C4" t="n">
-        <v>123.6069447031947</v>
+        <v>84.74446183058467</v>
       </c>
       <c r="D4" t="n">
-        <v>158.5512724881556</v>
+        <v>115.2346002813779</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.28311285838414</v>
+        <v>20.24854640009047</v>
       </c>
       <c r="C5" t="n">
-        <v>221.6786316189298</v>
+        <v>212.5729216620407</v>
       </c>
       <c r="D5" t="n">
-        <v>120.4358996184775</v>
+        <v>102.5190040159732</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>11.87423848286517</v>
       </c>
       <c r="C6" t="n">
-        <v>190.2293256610875</v>
+        <v>246.782902164225</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53470231257858</v>
+        <v>62.10830501376597</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.803331663981149</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>135.7629447771787</v>
+        <v>115.7009304408951</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>76.10508203321274</v>
+        <v>55.15949476310704</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
+        <v>25.90832191507333</v>
+      </c>
+      <c r="D10" t="n">
         <v>26.05067533218912</v>
-      </c>
-      <c r="D10" t="n">
-        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.527419501358789</v>
+        <v>0.2817615911188346</v>
       </c>
       <c r="C2" t="n">
-        <v>6.066219064541041</v>
+        <v>1.475566799482956</v>
       </c>
       <c r="D2" t="n">
-        <v>15.88762309782613</v>
+        <v>6.372524348266047</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38536918387927</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C3" t="n">
-        <v>33.43341806812513</v>
+        <v>15.15818455357075</v>
       </c>
       <c r="D3" t="n">
-        <v>74.37229733521711</v>
+        <v>51.07051557491908</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.18904500522568</v>
+        <v>12.57127935288041</v>
       </c>
       <c r="C4" t="n">
-        <v>117.4680763085394</v>
+        <v>67.45097602027711</v>
       </c>
       <c r="D4" t="n">
-        <v>162.0737832509932</v>
+        <v>112.8096834518882</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.78152189697203</v>
+        <v>19.02136176978195</v>
       </c>
       <c r="C5" t="n">
-        <v>226.2683021362837</v>
+        <v>167.6334205001429</v>
       </c>
       <c r="D5" t="n">
-        <v>143.3351648200344</v>
+        <v>106.9368686850839</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.47807974090175</v>
+        <v>11.83398682699105</v>
       </c>
       <c r="C6" t="n">
-        <v>261.9175247728938</v>
+        <v>239.2155908598906</v>
       </c>
       <c r="D6" t="n">
-        <v>72.17121898229578</v>
+        <v>65.81145735418494</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>196.0687610059475</v>
+        <v>162.4124862089583</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54323494228053</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>117.4121166893973</v>
+        <v>62.75331325545612</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>53.47187045950676</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.415099352447153</v>
+        <v>0.4928373475318988</v>
       </c>
       <c r="C2" t="n">
-        <v>3.277073836775853</v>
+        <v>6.047565858160352</v>
       </c>
       <c r="D2" t="n">
-        <v>11.76919147851076</v>
+        <v>7.154977268550754</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.70658060961722</v>
+        <v>1.875138115111408</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6095107600838</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="D3" t="n">
-        <v>71.64794745593223</v>
+        <v>44.31609136970102</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.21983903695583</v>
+        <v>8.959429548956392</v>
       </c>
       <c r="C4" t="n">
-        <v>105.2541531200048</v>
+        <v>50.15749020996954</v>
       </c>
       <c r="D4" t="n">
-        <v>162.5970547773567</v>
+        <v>113.2053277766997</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.10750319251098</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="C5" t="n">
-        <v>230.0971181828462</v>
+        <v>145.0041359172539</v>
       </c>
       <c r="D5" t="n">
-        <v>158.1104677689488</v>
+        <v>123.7492981203105</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.1258943569844</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C6" t="n">
-        <v>305.4698164286908</v>
+        <v>257.3690876591183</v>
       </c>
       <c r="D6" t="n">
-        <v>87.46684821446109</v>
+        <v>83.80394752991624</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>254.937298595699</v>
+        <v>259.0095880729147</v>
       </c>
       <c r="D7" t="n">
-        <v>45.27427712904591</v>
+        <v>45.39405034896402</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>152.5439582858694</v>
+        <v>141.8625432636641</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>61.12655730951914</v>
+        <v>54.35937038414588</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>23.85156047467625</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.828235209485814</v>
+        <v>0.5703954161673969</v>
       </c>
       <c r="C2" t="n">
-        <v>9.5111717587431</v>
+        <v>5.469316460358981</v>
       </c>
       <c r="D2" t="n">
-        <v>23.57078063126167</v>
+        <v>10.86991058142068</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.618984079761</v>
+        <v>1.762237129123025</v>
       </c>
       <c r="C3" t="n">
-        <v>21.83406894244906</v>
+        <v>17.22967220953152</v>
       </c>
       <c r="D3" t="n">
-        <v>66.21397391292612</v>
+        <v>40.03567137918493</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.11475097487241</v>
+        <v>6.215444715586556</v>
       </c>
       <c r="C4" t="n">
-        <v>91.39383903144832</v>
+        <v>35.83771819582557</v>
       </c>
       <c r="D4" t="n">
-        <v>159.2659848168473</v>
+        <v>109.0191555657913</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.42027979953821</v>
+        <v>16.93514789825748</v>
       </c>
       <c r="C5" t="n">
-        <v>214.4136986075034</v>
+        <v>117.7360934317988</v>
       </c>
       <c r="D5" t="n">
-        <v>174.0638679629595</v>
+        <v>136.217493964245</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.47056991663305</v>
+        <v>22.58117894538089</v>
       </c>
       <c r="C6" t="n">
-        <v>329.8623198884071</v>
+        <v>245.2935908968826</v>
       </c>
       <c r="D6" t="n">
-        <v>107.7536827750172</v>
+        <v>102.0781992967664</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.32069700858599</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>327.1605502063198</v>
+        <v>314.6442487248772</v>
       </c>
       <c r="D7" t="n">
-        <v>54.73636150257666</v>
+        <v>56.89227946110266</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>223.4752299177015</v>
+        <v>242.6683975357266</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>106.0562409943744</v>
+        <v>113.489052863227</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.956844158742146</v>
+        <v>4.102723656047421</v>
       </c>
       <c r="C2" t="n">
-        <v>4.52782041198629</v>
+        <v>6.415721247252906</v>
       </c>
       <c r="D2" t="n">
-        <v>7.322856125976958</v>
+        <v>7.329728359906686</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.526437753654543</v>
+        <v>0.7235480580298993</v>
       </c>
       <c r="C2" t="n">
-        <v>5.554728510628453</v>
+        <v>9.707521299592461</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53597749325652</v>
+        <v>16.82617390308608</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.99267010218054</v>
+        <v>1.821141991377833</v>
       </c>
       <c r="C3" t="n">
-        <v>29.34443887993716</v>
+        <v>19.15389770985527</v>
       </c>
       <c r="D3" t="n">
-        <v>74.86807992586175</v>
+        <v>39.28954312395735</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.98408071921636</v>
+        <v>4.824308218668826</v>
       </c>
       <c r="C4" t="n">
-        <v>129.0311007691583</v>
+        <v>38.95182191369645</v>
       </c>
       <c r="D4" t="n">
-        <v>162.3800885347182</v>
+        <v>104.8967969556589</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.7356164345839</v>
+        <v>13.67083678163684</v>
       </c>
       <c r="C5" t="n">
-        <v>297.4695543867836</v>
+        <v>92.77515805132359</v>
       </c>
       <c r="D5" t="n">
-        <v>158.1595551541612</v>
+        <v>142.0343491119073</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.44154978719959</v>
+        <v>23.10445047174444</v>
       </c>
       <c r="C6" t="n">
-        <v>273.6710082881366</v>
+        <v>219.8545443844393</v>
       </c>
       <c r="D6" t="n">
-        <v>83.07941772418209</v>
+        <v>119.3059080108894</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>157.1424645325614</v>
+        <v>333.0893245922663</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>70.24699348197203</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>78.10784734987622</v>
+        <v>325.0321211835127</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>197.3577957416235</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>83.13439559561991</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.479534848028949</v>
+        <v>4.504258467084366</v>
       </c>
       <c r="C2" t="n">
-        <v>4.757549374780043</v>
+        <v>5.197372346282614</v>
       </c>
       <c r="D2" t="n">
-        <v>12.96790542539612</v>
+        <v>11.48153940116645</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.53415286656828</v>
+        <v>6.778967897824225</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5895316486336</v>
+        <v>12.66454538478385</v>
       </c>
       <c r="D3" t="n">
-        <v>9.58185759344887</v>
+        <v>8.050331174823844</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39911796873997</v>
+        <v>11.67864763485898</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14832348340339</v>
+        <v>59.95039119227609</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576366819851761</v>
+        <v>0.7785765089905985</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.12726734865359</v>
+        <v>2.976659039276329</v>
       </c>
       <c r="C2" t="n">
-        <v>3.987859174650544</v>
+        <v>3.095450511490193</v>
       </c>
       <c r="D2" t="n">
-        <v>18.60215550006856</v>
+        <v>11.31856928226148</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61255381418778</v>
+        <v>12.38474728907351</v>
       </c>
       <c r="C3" t="n">
-        <v>16.02212253330795</v>
+        <v>17.76472470834603</v>
       </c>
       <c r="D3" t="n">
-        <v>18.15742379004476</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.32878766993144</v>
+        <v>8.474446183058468</v>
       </c>
       <c r="C4" t="n">
-        <v>18.49318150489717</v>
+        <v>21.14782729718054</v>
       </c>
       <c r="D4" t="n">
-        <v>20.08852152429823</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44484297386989</v>
+        <v>13.63249924060765</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16596606474783</v>
+        <v>73.77587824328845</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251545889235767</v>
+        <v>1.603823440071488</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.43888228152733</v>
+        <v>2.511310627463341</v>
       </c>
       <c r="C2" t="n">
-        <v>5.937610115284709</v>
+        <v>9.367836593923064</v>
       </c>
       <c r="D2" t="n">
-        <v>30.07682266730528</v>
+        <v>18.03568707471815</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90431280879833</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C3" t="n">
-        <v>15.7128720064702</v>
+        <v>14.10771451002667</v>
       </c>
       <c r="D3" t="n">
-        <v>28.82411259668635</v>
+        <v>21.73589417202438</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.56823629877643</v>
+        <v>18.07201173977529</v>
       </c>
       <c r="C4" t="n">
-        <v>31.03893541746715</v>
+        <v>35.85048091598077</v>
       </c>
       <c r="D4" t="n">
-        <v>24.68310078017331</v>
+        <v>22.41133659254619</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.21646752101981</v>
+        <v>8.222137023067038</v>
       </c>
       <c r="C5" t="n">
-        <v>22.06477965294707</v>
+        <v>25.79542092908495</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>26.70353755551325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74359993623748</v>
+        <v>14.84967721381148</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1359596110486</v>
+        <v>87.44809914800095</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023079980871243</v>
+        <v>2.474946202301914</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.436918786118836</v>
+        <v>2.017491532227195</v>
       </c>
       <c r="C2" t="n">
-        <v>5.838453597155781</v>
+        <v>5.820782138479339</v>
       </c>
       <c r="D2" t="n">
-        <v>33.5816619714664</v>
+        <v>27.73633614038089</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.40638679629595</v>
+        <v>9.822385780989338</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0227444281137</v>
+        <v>28.13688920371358</v>
       </c>
       <c r="D3" t="n">
-        <v>45.26838664282042</v>
+        <v>31.63191103083223</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.86101809882023</v>
+        <v>20.57350489019616</v>
       </c>
       <c r="C4" t="n">
-        <v>35.76114187489431</v>
+        <v>35.5824637927214</v>
       </c>
       <c r="D4" t="n">
-        <v>32.85124167950677</v>
+        <v>28.60125586782233</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.29825568010856</v>
+        <v>18.53048791765855</v>
       </c>
       <c r="C5" t="n">
-        <v>41.45429681182157</v>
+        <v>49.67643383488862</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>29.03518835309942</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.54593383901924</v>
+        <v>8.090582830697967</v>
       </c>
       <c r="C6" t="n">
-        <v>24.11074186859742</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.48937768726721</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07600744360855</v>
+        <v>16.10274673942818</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9244295130653</v>
+        <v>101.7015583542833</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886098073755636</v>
+        <v>3.390051945142776</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.698464586075987</v>
+        <v>3.19166178650638</v>
       </c>
       <c r="C2" t="n">
-        <v>9.309913479372502</v>
+        <v>6.982189672603315</v>
       </c>
       <c r="D2" t="n">
-        <v>35.48723426540946</v>
+        <v>22.15313694632928</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.19392838155114</v>
+        <v>8.222137023067038</v>
       </c>
       <c r="C3" t="n">
-        <v>20.29763378530281</v>
+        <v>24.84803439448677</v>
       </c>
       <c r="D3" t="n">
-        <v>57.12299017160066</v>
+        <v>46.48084505756524</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.83250635766807</v>
+        <v>19.89708072197011</v>
       </c>
       <c r="C4" t="n">
-        <v>36.82044764777662</v>
+        <v>55.76032435810609</v>
       </c>
       <c r="D4" t="n">
-        <v>41.04490801915065</v>
+        <v>38.02014334236623</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.29763378530281</v>
+        <v>24.91184799526282</v>
       </c>
       <c r="C5" t="n">
-        <v>40.54618018539328</v>
+        <v>58.70851271395927</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>32.88854809226815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>16.86544381125596</v>
       </c>
       <c r="C6" t="n">
-        <v>31.43654323768712</v>
+        <v>55.2655235151657</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>18.26541603751191</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.162496759482</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06750117283307</v>
+        <v>17.38447787946155</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14126114191416</v>
+        <v>115.6067778984193</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300625879624802</v>
+        <v>4.346119469865386</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.262568605390403</v>
+        <v>2.276672926148354</v>
       </c>
       <c r="C2" t="n">
-        <v>7.250206795862695</v>
+        <v>13.50590316732337</v>
       </c>
       <c r="D2" t="n">
-        <v>25.70510014029423</v>
+        <v>26.37661556999905</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.6854241284803</v>
+        <v>9.724211010564657</v>
       </c>
       <c r="C3" t="n">
-        <v>30.84651286743478</v>
+        <v>26.09485397888022</v>
       </c>
       <c r="D3" t="n">
-        <v>73.99923320760334</v>
+        <v>53.42180132659018</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.34600146471816</v>
+        <v>17.68913013511903</v>
       </c>
       <c r="C4" t="n">
-        <v>45.84369079750906</v>
+        <v>59.27007240078844</v>
       </c>
       <c r="D4" t="n">
-        <v>62.48627787990099</v>
+        <v>50.80838893788518</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.81429511964389</v>
+        <v>27.68528525976006</v>
       </c>
       <c r="C5" t="n">
-        <v>57.70222131710629</v>
+        <v>82.17228284545804</v>
       </c>
       <c r="D5" t="n">
-        <v>38.75449062514284</v>
+        <v>38.82812170296135</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.09186767803848</v>
+        <v>25.03652995370216</v>
       </c>
       <c r="C6" t="n">
-        <v>51.24035792775378</v>
+        <v>74.74732495823942</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>37.35353665118265</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>34.43480072645687</v>
+        <v>54.5567016726995</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>22.1138670381594</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.04999668412111</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.65056423721292</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.293062744257213</v>
+        <v>18.69021003803435</v>
       </c>
       <c r="C21" t="n">
-        <v>77.48879165773289</v>
+        <v>129.0514502626181</v>
       </c>
       <c r="D21" t="n">
-        <v>6.381429901225061</v>
+        <v>5.340060010866958</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.480696522182442</v>
+        <v>2.102903582496668</v>
       </c>
       <c r="C2" t="n">
-        <v>5.847289326494002</v>
+        <v>8.103345550853172</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99199145411256</v>
+        <v>20.57055964708342</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.33337761328319</v>
+        <v>12.66945412330509</v>
       </c>
       <c r="C3" t="n">
-        <v>29.24135537099124</v>
+        <v>45.77398671050754</v>
       </c>
       <c r="D3" t="n">
-        <v>77.39117152577607</v>
+        <v>59.1895690890402</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>13.29875440172729</v>
       </c>
       <c r="C4" t="n">
-        <v>64.66870302644165</v>
+        <v>79.14162768244812</v>
       </c>
       <c r="D4" t="n">
-        <v>84.92313991275759</v>
+        <v>48.48557386963722</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.3982961349505</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C5" t="n">
-        <v>73.45927197026759</v>
+        <v>44.64497685062371</v>
       </c>
       <c r="D5" t="n">
-        <v>53.18618187757097</v>
+        <v>33.87029579651497</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.23528495831652</v>
+        <v>8.734609324683873</v>
       </c>
       <c r="C6" t="n">
-        <v>73.94229184075704</v>
+        <v>35.90447703971436</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>25.88181472705867</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>56.17364014159399</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>27.78738702100172</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>35.46563581591602</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.70630287217673</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.506700070815319</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.26538832322808</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.506700070815319</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
